--- a/Elli/students_code45.xlsx
+++ b/Elli/students_code45.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellemarouda/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slabr\source\github\np3\Elli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2A1D26-8A1A-274E-AFD4-A6087A62EB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE05FD35-905A-4D98-A06A-37D9CB63D5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" xr2:uid="{D0CD93E6-F513-664B-B487-89E63346EE74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0CD93E6-F513-664B-B487-89E63346EE74}"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="51">
   <si>
     <t>student_id</t>
   </si>
@@ -419,7 +420,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -489,8 +490,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
-    <cellStyle name="Υπερ-σύνδεση" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -506,7 +507,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Θέμα του Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -823,13 +824,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EE6484-2DA2-7341-8A68-5DAF5D5F413B}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="40.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.375" customWidth="1"/>
+    <col min="4" max="4" width="84.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="40.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +858,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="40.5" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -876,7 +878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="40.5" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -896,7 +898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="40.5" customHeight="1">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -916,7 +918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="40.5" customHeight="1">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -936,7 +938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="40.5" customHeight="1">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -956,7 +958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="356" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="40.5" customHeight="1">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -976,7 +978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="40.5" customHeight="1">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -996,7 +998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="40.5" customHeight="1">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1016,7 +1018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="40.5" customHeight="1">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1036,7 +1038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="40.5" customHeight="1">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1056,7 +1058,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="40.5" customHeight="1">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1076,7 +1078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="40.5" customHeight="1">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1096,7 +1098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="40.5" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1116,7 +1118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="40.5" customHeight="1">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1136,7 +1138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="40.5" customHeight="1">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1156,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="40.5" customHeight="1">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1176,7 +1178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="40.5" customHeight="1">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1196,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="40.5" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -1216,7 +1218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="40.5" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -1230,13 +1232,13 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="40.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1250,13 +1252,13 @@
         <v>39</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="40.5" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1270,13 +1272,13 @@
         <v>41</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="356" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="40.5" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
@@ -1290,13 +1292,13 @@
         <v>43</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="40.5" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
@@ -1310,13 +1312,13 @@
         <v>45</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="40.5" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -1330,13 +1332,13 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="40.5" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
@@ -1386,4 +1388,561 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB994392-43A7-427E-9335-365B4C74AF08}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="409.5">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.5">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="409.5">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="409.5">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="409.5">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="346.5">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="409.5">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="409.5">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="409.5">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="409.5">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="409.5">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="409.5">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="409.5">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="409.5">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="409.5">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="409.5">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="409.5">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="409.5">
+      <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="409.5">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="409.5">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="409.5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="346.5">
+      <c r="A23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="409.5">
+      <c r="A24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="409.5">
+      <c r="A25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="409.5">
+      <c r="A26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="http://localhost:8888/moodle501/user/view.php?id=8&amp;course=10" xr:uid="{97D2ECA0-8490-4B4D-A4D0-5ECD00156AB2}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{9D99CDE0-E96B-4FBD-9EF4-7259F02CD5CC}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{2DF383D9-578F-4EEA-AE6F-985CBAE33B0F}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{87616D6C-B8CF-41C7-A150-46E6007E556F}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{8407CDFE-847A-4B1F-951C-1A9238EEDC43}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{79966B62-4FD2-41E5-BC55-02782945A57D}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{00CFE32E-BEC8-4529-8F39-7FD12E062A1F}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{F51E155B-EAD4-402B-A57F-9491304DC5D9}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{6737E798-ACF4-45E6-A0B0-44E95F4B7DDA}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{810C6668-E054-4D43-9F96-E5C98413BCA8}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{C350A0B2-ECB8-4811-B016-24118F120812}"/>
+    <hyperlink ref="A14" r:id="rId12" display="http://localhost:8888/moodle501/user/view.php?id=78&amp;course=10" xr:uid="{0ED55CFB-6A47-4C18-BB31-230F1997D9FB}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{DCAA3908-AF28-4947-9FC4-1FA956F58BED}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{C944D971-EEDD-4F2A-B31C-567D23F13FC5}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{EFD3037D-2545-4C5A-8A08-8464862A15C1}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{52E4726D-06C1-43ED-9719-77DBB572CEFD}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{92AD7F4C-2F02-4536-9F16-56424313B938}"/>
+    <hyperlink ref="A19" r:id="rId18" display="http://localhost:8888/moodle501/user/view.php?id=8&amp;course=10" xr:uid="{6A811807-D788-4BD4-9010-638E4B2BBAF4}"/>
+    <hyperlink ref="A20" r:id="rId19" display="http://localhost:8888/moodle501/user/view.php?id=57&amp;course=10" xr:uid="{71C37C87-C6D0-44BB-AE97-14F1F0E1C58E}"/>
+    <hyperlink ref="A21" r:id="rId20" display="http://localhost:8888/moodle501/user/view.php?id=77&amp;course=10" xr:uid="{E1737D39-1E8D-451A-8A87-35D05109D5D9}"/>
+    <hyperlink ref="A22" r:id="rId21" display="http://localhost:8888/moodle501/user/view.php?id=78&amp;course=10" xr:uid="{5EAD1C00-1159-4A4B-B302-2EAA5FDBECD3}"/>
+    <hyperlink ref="A23" r:id="rId22" display="http://localhost:8888/moodle501/user/view.php?id=79&amp;course=10" xr:uid="{EF68A1D0-3869-4887-8C3D-CBE1C9C5AE1D}"/>
+    <hyperlink ref="A24" r:id="rId23" display="http://localhost:8888/moodle501/user/view.php?id=80&amp;course=10" xr:uid="{26C615B2-3194-4077-94E6-0EF036FCC0AC}"/>
+    <hyperlink ref="A25" r:id="rId24" display="http://localhost:8888/moodle501/user/view.php?id=81&amp;course=10" xr:uid="{E3BC0168-81D7-4661-B1FB-9A47128B0BE5}"/>
+    <hyperlink ref="A26" r:id="rId25" display="http://localhost:8888/moodle501/user/view.php?id=82&amp;course=10" xr:uid="{DD9D757B-A7AF-494F-9D07-9D7315ED4801}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Elli/students_code45.xlsx
+++ b/Elli/students_code45.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slabr\source\github\np3\Elli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellemarouda/Desktop/np3/np3/Elli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE05FD35-905A-4D98-A06A-37D9CB63D5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA14DF65-1C63-5C42-8EF0-587BFFE4860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0CD93E6-F513-664B-B487-89E63346EE74}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15720" xr2:uid="{D0CD93E6-F513-664B-B487-89E63346EE74}"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="54">
   <si>
     <t>student_id</t>
   </si>
@@ -415,12 +415,35 @@
 if __name__ == "__main__":
     main()</t>
   </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>emarouda@outlook.com.gr</t>
+  </si>
+  <si>
+    <t>1: def evenlist(values):
+2:     even_numbers = [num for num in values if num % 2 == 0]
+3:     return even_numbers
+4:
+5:
+6: while True:
+7:     num = input("give numbers with space: ")
+8:
+9:     try:
+10:         nlist = [int(x) for x in num.split()]
+11:     except ValueError:
+12:         print("Please give only numbers.")
+13:         continue
+14:
+15:     result = evenlist(nlist)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -490,8 +513,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Υπερ-σύνδεση" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -507,7 +530,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Θέμα του Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -823,15 +846,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EE6484-2DA2-7341-8A68-5DAF5D5F413B}">
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="40.5" customHeight="1"/>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
-    <col min="2" max="2" width="25.375" customWidth="1"/>
-    <col min="4" max="4" width="84.625" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="84.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="40.5" customHeight="1">
+    <row r="1" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +881,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1">
+    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -878,7 +901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="40.5" customHeight="1">
+    <row r="3" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -898,7 +921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="40.5" customHeight="1">
+    <row r="4" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -918,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="40.5" customHeight="1">
+    <row r="5" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -938,7 +961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="40.5" customHeight="1">
+    <row r="6" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -958,7 +981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="40.5" customHeight="1">
+    <row r="7" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -978,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="40.5" customHeight="1">
+    <row r="8" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -998,7 +1021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="40.5" customHeight="1">
+    <row r="9" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1018,7 +1041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="40.5" customHeight="1">
+    <row r="10" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1038,7 +1061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="40.5" customHeight="1">
+    <row r="11" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1058,7 +1081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="40.5" customHeight="1">
+    <row r="12" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1078,7 +1101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="40.5" customHeight="1">
+    <row r="13" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1098,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="40.5" customHeight="1">
+    <row r="14" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1118,7 +1141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="40.5" customHeight="1">
+    <row r="15" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1138,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="40.5" customHeight="1">
+    <row r="16" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1158,7 +1181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="40.5" customHeight="1">
+    <row r="17" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1201,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="40.5" customHeight="1">
+    <row r="18" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1198,7 +1221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="40.5" customHeight="1">
+    <row r="19" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -1218,7 +1241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="40.5" customHeight="1">
+    <row r="20" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -1238,7 +1261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="40.5" customHeight="1">
+    <row r="21" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1258,7 +1281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="40.5" customHeight="1">
+    <row r="22" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1278,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="40.5" customHeight="1">
+    <row r="23" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
@@ -1298,7 +1321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="40.5" customHeight="1">
+    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
@@ -1318,7 +1341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="40.5" customHeight="1">
+    <row r="25" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -1338,7 +1361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="40.5" customHeight="1">
+    <row r="26" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
@@ -1352,10 +1375,30 @@
         <v>49</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1385,6 +1428,7 @@
     <hyperlink ref="A24" r:id="rId23" display="http://localhost:8888/moodle501/user/view.php?id=80&amp;course=10" xr:uid="{D166B788-0978-C24D-9DE4-3D4D434DC18F}"/>
     <hyperlink ref="A25" r:id="rId24" display="http://localhost:8888/moodle501/user/view.php?id=81&amp;course=10" xr:uid="{CAF4B94D-3912-4D40-8B20-5D11AD0834AB}"/>
     <hyperlink ref="A26" r:id="rId25" display="http://localhost:8888/moodle501/user/view.php?id=82&amp;course=10" xr:uid="{3D625922-E172-B742-A84C-194BB815D3C6}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{5431D43B-DBD4-5B4A-9B84-37C9C8662BC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1393,9 +1437,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB994392-43A7-427E-9335-365B4C74AF08}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,7 +1459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="409.5">
+    <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1435,7 +1479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="409.5">
+    <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1455,7 +1499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="409.5">
+    <row r="4" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1475,7 +1519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="409.5">
+    <row r="5" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1495,7 +1539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="409.5">
+    <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1515,7 +1559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="346.5">
+    <row r="7" spans="1:6" ht="372" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1535,7 +1579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="409.5">
+    <row r="8" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1555,7 +1599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="409.5">
+    <row r="9" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1575,7 +1619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="409.5">
+    <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1595,7 +1639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="409.5">
+    <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1615,7 +1659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="409.5">
+    <row r="12" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1635,7 +1679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="409.5">
+    <row r="13" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1655,7 +1699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="409.5">
+    <row r="14" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1675,7 +1719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="409.5">
+    <row r="15" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1695,7 +1739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="409.5">
+    <row r="16" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1715,7 +1759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="409.5">
+    <row r="17" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1735,7 +1779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="409.5">
+    <row r="18" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1755,7 +1799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="409.5">
+    <row r="19" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -1775,7 +1819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="409.5">
+    <row r="20" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -1795,7 +1839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="409.5">
+    <row r="21" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1815,7 +1859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="409.5">
+    <row r="22" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1835,7 +1879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="346.5">
+    <row r="23" spans="1:6" ht="372" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
@@ -1855,7 +1899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="409.5">
+    <row r="24" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
@@ -1875,7 +1919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="409.5">
+    <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -1895,7 +1939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="409.5">
+    <row r="26" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
